--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R234cbc5fa2bc4086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R9047a2d51f154491"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -415,17 +415,17 @@
         <x:v>模型问题</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="15" t="n">
         <x:f>SUM(B8:D8)</x:f>
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
         <x:v>角色网格、服装形体、蒙皮绑定及模型穿插。</x:v>
@@ -562,17 +562,17 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -604,17 +604,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +634,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -662,24 +662,24 @@
       <x:c r="E20" s="18"/>
       <x:c r="F20" s="18"/>
     </x:row>
-    <x:row r="21" ht="36" customHeight="1">
+    <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="17" t="str">
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>将 31 个原事项拆为 82 个独立子事项，分为 10 种类型并各用独立文件。White 换装已最终交付，源清单差异与未验收事项继续追踪。</x:v>
+        <x:v>新增 scene 性能诊断交付与 4 个待确认瓶颈，更新 VSM 和性能目标证据；补录 Purple 身体恢复、旧 Miyako 袖部交付与 2 个范围或保存缺口。White 新校服仍已最终交付。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
       <x:c r="E21" s="18"/>
       <x:c r="F21" s="18"/>
     </x:row>
-    <x:row r="22" ht="36" customHeight="1">
+    <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="17" t="str">
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>近期可访问项目聊天及项目完成、验证记录；非完整历史穷举</x:v>
+        <x:v>本轮查看近期 50 条聊天，读取 23 个候选或关联聊天的最新 2–5 回合；部分有更早回合未读取，逐聊天保存游标。结合对应交付和验证文件，非完整历史穷举。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -763,6 +763,18 @@
       <x:c r="D29" s="9"/>
       <x:c r="E29" s="9"/>
       <x:c r="F29" s="9"/>
+    </x:row>
+    <x:row r="30" ht="59" customHeight="1">
+      <x:c r="A30" s="20" t="n">
+        <x:v>46296.382731481484</x:v>
+      </x:c>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="9" t="str">
+        <x:v>新增 scene 性能诊断交付与 4 个待确认瓶颈，更新 VSM 和性能目标证据；补录 Purple 身体恢复、旧 Miyako 袖部交付与 2 个范围或保存缺口。White 新校服仍已最终交付。 本轮新增 10 项，更新 3 项；原有待确认事项按最新证据保留，无正在实施的新证据。</x:v>
+      </x:c>
+      <x:c r="D30" s="9"/>
+      <x:c r="E30" s="9"/>
+      <x:c r="F30" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -777,6 +789,8 @@
     <x:mergeCell ref="C28:F28"/>
     <x:mergeCell ref="A29:B29"/>
     <x:mergeCell ref="C29:F29"/>
+    <x:mergeCell ref="A30:B30"/>
+    <x:mergeCell ref="C30:F30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R9047a2d51f154491"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rb7c546ac23bd406f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
+        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -415,7 +415,7 @@
         <x:v>模型问题</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="15" t="n">
         <x:v>0</x:v>
@@ -425,7 +425,7 @@
       </x:c>
       <x:c r="E8" s="15" t="n">
         <x:f>SUM(B8:D8)</x:f>
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
         <x:v>角色网格、服装形体、蒙皮绑定及模型穿插。</x:v>
@@ -457,17 +457,17 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>布料、贴图遮罩、人物着色及真实游戏画面。</x:v>
@@ -478,7 +478,7 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
@@ -488,7 +488,7 @@
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -520,17 +520,17 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -541,7 +541,7 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
@@ -551,7 +551,7 @@
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -562,17 +562,17 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -604,17 +604,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +634,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>92</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>新增 scene 性能诊断交付与 4 个待确认瓶颈，更新 VSM 和性能目标证据；补录 Purple 身体恢复、旧 Miyako 袖部交付与 2 个范围或保存缺口。White 新校服仍已最终交付。</x:v>
+        <x:v>综合楼景观参考图及园路、草坪、花境、设施和地面采样已交付；严格一比一与角色实走待确认。远景Nanite和投影关闭已保存回读；VSM收益复测与光追池警告仍待确认。补齐上次中断后的表格验收与Git同步。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +679,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>本轮查看近期 50 条聊天，读取 23 个候选或关联聊天的最新 2–5 回合；部分有更早回合未读取，逐聊天保存游标。结合对应交付和验证文件，非完整历史穷举。</x:v>
+        <x:v>本轮查看近期50条聊天，读取12个新增、更新、待确认或中断来源聊天最新2–6回合；逐聊天保存游标，非完整历史遍历。保留不在列表中的已知基线。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -775,6 +775,30 @@
       <x:c r="D30" s="9"/>
       <x:c r="E30" s="9"/>
       <x:c r="F30" s="9"/>
+    </x:row>
+    <x:row r="31" ht="59" customHeight="1">
+      <x:c r="A31" s="20" t="n">
+        <x:v>46297.38238425926</x:v>
+      </x:c>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="9" t="str">
+        <x:v>White 下沉自动恢复与服装形体、权重修正已交付；更新最新 30 人及 94 帧验收。补录 Shipping 诊断包基准与 MD 报告；标准打包 GameFeatureData 错误、实际显示和像素验收及渲染根因仍待确认。 本轮新增 11 项、更新 7 项，无正在实施证据。</x:v>
+      </x:c>
+      <x:c r="D31" s="9"/>
+      <x:c r="E31" s="9"/>
+      <x:c r="F31" s="9"/>
+    </x:row>
+    <x:row r="32" ht="59" customHeight="1">
+      <x:c r="A32" s="20" t="n">
+        <x:v>46298.38186342592</x:v>
+      </x:c>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="9" t="str">
+        <x:v>综合楼景观参考图及园路、草坪、花境、设施和地面采样已交付；严格一比一与角色实走待确认。远景Nanite和投影关闭已保存回读；VSM收益复测与光追池警告仍待确认。补齐上次中断后的表格验收与Git同步。 本轮新增16项、更新1项；未发现正在实施证据。</x:v>
+      </x:c>
+      <x:c r="D32" s="9"/>
+      <x:c r="E32" s="9"/>
+      <x:c r="F32" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -791,6 +815,10 @@
     <x:mergeCell ref="C29:F29"/>
     <x:mergeCell ref="A30:B30"/>
     <x:mergeCell ref="C30:F30"/>
+    <x:mergeCell ref="A31:B31"/>
+    <x:mergeCell ref="C31:F31"/>
+    <x:mergeCell ref="A32:B32"/>
+    <x:mergeCell ref="C32:F32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rb7c546ac23bd406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rfbb49b53f68a4b26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -436,7 +436,7 @@
         <x:v>动画问题</x:v>
       </x:c>
       <x:c r="B9" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="15" t="n">
         <x:v>0</x:v>
@@ -446,7 +446,7 @@
       </x:c>
       <x:c r="E9" s="15" t="n">
         <x:f>SUM(B9:D9)</x:f>
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
         <x:v>动作循环、播放同步、骨段变化及动画复核。</x:v>
@@ -457,17 +457,17 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>布料、贴图遮罩、人物着色及真实游戏画面。</x:v>
@@ -478,7 +478,7 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
@@ -488,7 +488,7 @@
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -499,7 +499,7 @@
         <x:v>交互与AI</x:v>
       </x:c>
       <x:c r="B12" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="15" t="n">
         <x:v>0</x:v>
@@ -509,7 +509,7 @@
       </x:c>
       <x:c r="E12" s="15" t="n">
         <x:f>SUM(B12:D12)</x:f>
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>门交互部署、学生接入、寻路及人群避让。</x:v>
@@ -541,17 +541,17 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -562,7 +562,7 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
@@ -572,7 +572,7 @@
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -583,7 +583,7 @@
         <x:v>游戏设计</x:v>
       </x:c>
       <x:c r="B16" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C16" s="15" t="n">
         <x:v>0</x:v>
@@ -593,7 +593,7 @@
       </x:c>
       <x:c r="E16" s="15" t="n">
         <x:f>SUM(B16:D16)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
         <x:v>操作与交互规则、自由探索范围、内容文案及完成判定。</x:v>
@@ -604,7 +604,7 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
@@ -614,7 +614,7 @@
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>90</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +634,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>119</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>综合楼景观参考图及园路、草坪、花境、设施和地面采样已交付；严格一比一与角色实走待确认。远景Nanite和投影关闭已保存回读；VSM收益复测与光追池警告仍待确认。补齐上次中断后的表格验收与Git同步。</x:v>
+        <x:v>单White、观察入口、C++迁移、自然动作/坐姿与体力寻座、跨校园上下楼已交付。风动、花坛和食堂碰撞修复完成。10月3日Shipping发布通过并获用户确认；原工程规则、后续版本发布同步及观察模式手柄适用范围仍待确认。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +679,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>本轮查看近期50条聊天，读取12个新增、更新、待确认或中断来源聊天最新2–6回合；逐聊天保存游标，非完整历史遍历。保留不在列表中的已知基线。</x:v>
+        <x:v>查看近期50条聊天，成功读取21个来源聊天最新1–4回合；另1个历史聊天读取两次失败，保留已确认基线。保存逐聊天游标，未遍历全部历史。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -799,6 +799,18 @@
       <x:c r="D32" s="9"/>
       <x:c r="E32" s="9"/>
       <x:c r="F32" s="9"/>
+    </x:row>
+    <x:row r="33" ht="59" customHeight="1">
+      <x:c r="A33" s="20" t="n">
+        <x:v>46299.386030092595</x:v>
+      </x:c>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="9" t="str">
+        <x:v>单White、观察入口、C++迁移、自然动作/坐姿与体力寻座、跨校园上下楼已交付。风动、花坛和食堂碰撞修复完成。10月3日Shipping发布通过并获用户确认；原工程规则、后续版本发布同步及观察模式手柄适用范围仍待确认。 新增52项，修订17项；进行中为0。</x:v>
+      </x:c>
+      <x:c r="D33" s="9"/>
+      <x:c r="E33" s="9"/>
+      <x:c r="F33" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -819,6 +831,8 @@
     <x:mergeCell ref="C31:F31"/>
     <x:mergeCell ref="A32:B32"/>
     <x:mergeCell ref="C32:F32"/>
+    <x:mergeCell ref="A33:B33"/>
+    <x:mergeCell ref="C33:F33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rfbb49b53f68a4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Re6558a7daf0442e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:15:03（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -457,7 +457,7 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
@@ -467,7 +467,7 @@
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>布料、贴图遮罩、人物着色及真实游戏画面。</x:v>
@@ -478,17 +478,17 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -499,7 +499,7 @@
         <x:v>交互与AI</x:v>
       </x:c>
       <x:c r="B12" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="15" t="n">
         <x:v>0</x:v>
@@ -509,7 +509,7 @@
       </x:c>
       <x:c r="E12" s="15" t="n">
         <x:f>SUM(B12:D12)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>门交互部署、学生接入、寻路及人群避让。</x:v>
@@ -520,17 +520,17 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -541,7 +541,7 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
@@ -551,7 +551,7 @@
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -562,17 +562,17 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -583,7 +583,7 @@
         <x:v>游戏设计</x:v>
       </x:c>
       <x:c r="B16" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="15" t="n">
         <x:v>0</x:v>
@@ -593,7 +593,7 @@
       </x:c>
       <x:c r="E16" s="15" t="n">
         <x:f>SUM(B16:D16)</x:f>
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
         <x:v>操作与交互规则、自由探索范围、内容文案及完成判定。</x:v>
@@ -604,17 +604,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>140</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +634,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>171</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>单White、观察入口、C++迁移、自然动作/坐姿与体力寻座、跨校园上下楼已交付。风动、花坛和食堂碰撞修复完成。10月3日Shipping发布通过并获用户确认；原工程规则、后续版本发布同步及观察模式手柄适用范围仍待确认。</x:v>
+        <x:v>第一人称入口与新包、高三门、长廊V2、遮阳棚、棕榈、校训和夜景/昼夜系统分阶段交付。原工程打包规则缺口已关闭。29厕位门洞通行、夜景细节、当前帧耗显存和最新白天修订发布同步仍待确认。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +679,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>查看近期50条聊天，成功读取21个来源聊天最新1–4回合；另1个历史聊天读取两次失败，保留已确认基线。保存逐聊天游标，未遍历全部历史。</x:v>
+        <x:v>查看近期50条聊天，成功读取40个来源/候选聊天最新1–6回合，另1历史聊天读取MCP -32000失败并保留基线。部分有更早回合未读取，非全历史遍历。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -811,6 +811,18 @@
       <x:c r="D33" s="9"/>
       <x:c r="E33" s="9"/>
       <x:c r="F33" s="9"/>
+    </x:row>
+    <x:row r="34" ht="59" customHeight="1">
+      <x:c r="A34" s="20" t="n">
+        <x:v>46300.38545138889</x:v>
+      </x:c>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="9" t="str">
+        <x:v>第一人称入口与新包、高三门、长廊V2、遮阳棚、棕榈、校训和夜景/昼夜系统分阶段交付。原工程打包规则缺口已关闭。29厕位门洞通行、夜景细节、当前帧耗显存和最新白天修订发布同步仍待确认。 新增46项，修订15项；进行中0项。</x:v>
+      </x:c>
+      <x:c r="D34" s="9"/>
+      <x:c r="E34" s="9"/>
+      <x:c r="F34" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -833,6 +845,8 @@
     <x:mergeCell ref="C32:F32"/>
     <x:mergeCell ref="A33:B33"/>
     <x:mergeCell ref="C33:F33"/>
+    <x:mergeCell ref="A34:B34"/>
+    <x:mergeCell ref="C34:F34"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Re6558a7daf0442e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R3cc58be4e2ef44fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:15:03（北京时间）</x:v>
+        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -457,7 +457,7 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
@@ -467,10 +467,10 @@
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>布料、贴图遮罩、人物着色及真实游戏画面。</x:v>
+        <x:v>角色、建筑与环境的材质、贴图、天空光照及渲染效果。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
@@ -478,7 +478,7 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
@@ -488,7 +488,7 @@
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -520,7 +520,7 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
@@ -530,7 +530,7 @@
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -541,17 +541,17 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -562,17 +562,17 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="15" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -604,7 +604,7 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
@@ -614,7 +614,7 @@
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>183</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +634,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>217</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>第一人称入口与新包、高三门、长廊V2、遮阳棚、棕榈、校训和夜景/昼夜系统分阶段交付。原工程打包规则缺口已关闭。29厕位门洞通行、夜景细节、当前帧耗显存和最新白天修订发布同步仍待确认。</x:v>
+        <x:v>时间面板、体积云和黑天空修复、月亮、黄昏提前缓亮、教学楼材质及密铺草地分阶段交付。凌晨版本发布缺口关闭；最新材质与草地发布、草地实测及昼夜说明同步待确认。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +679,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>查看近期50条聊天，成功读取40个来源/候选聊天最新1–6回合，另1历史聊天读取MCP -32000失败并保留基线。部分有更早回合未读取，非全历史遍历。</x:v>
+        <x:v>查看近期50条聊天，读取32个新、更新或待确认来源聊天最新1–6回合；更早回合未全读，非全历史遍历。未列出聊天保留已确认基线。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -823,6 +823,18 @@
       <x:c r="D34" s="9"/>
       <x:c r="E34" s="9"/>
       <x:c r="F34" s="9"/>
+    </x:row>
+    <x:row r="35" ht="44" customHeight="1">
+      <x:c r="A35" s="20" t="n">
+        <x:v>46301.38113425926</x:v>
+      </x:c>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="9" t="str">
+        <x:v>时间面板、体积云和黑天空修复、月亮、黄昏提前缓亮、教学楼材质及密铺草地分阶段交付。凌晨版本发布缺口关闭；最新材质与草地发布、草地实测及昼夜说明同步待确认。 新增21项，修订13项；进行中0项。</x:v>
+      </x:c>
+      <x:c r="D35" s="9"/>
+      <x:c r="E35" s="9"/>
+      <x:c r="F35" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -847,6 +859,8 @@
     <x:mergeCell ref="C33:F33"/>
     <x:mergeCell ref="A34:B34"/>
     <x:mergeCell ref="C34:F34"/>
+    <x:mergeCell ref="A35:B35"/>
+    <x:mergeCell ref="C35:F35"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R3cc58be4e2ef44fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R7eb86a632ca34606"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -457,7 +457,7 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
@@ -467,7 +467,7 @@
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>角色、建筑与环境的材质、贴图、天空光照及渲染效果。</x:v>
@@ -520,7 +520,7 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
@@ -530,7 +530,7 @@
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -541,13 +541,13 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
@@ -562,7 +562,7 @@
         <x:v>性能问题</x:v>
       </x:c>
       <x:c r="B15" s="15" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="15" t="n">
         <x:v>0</x:v>
@@ -572,7 +572,7 @@
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -604,17 +604,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +626,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>202</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -638,7 +638,7 @@
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>238</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +667,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>时间面板、体积云和黑天空修复、月亮、黄昏提前缓亮、教学楼材质及密铺草地分阶段交付。凌晨版本发布缺口关闭；最新材质与草地发布、草地实测及昼夜说明同步待确认。</x:v>
+        <x:v>150名White、四级LOD与屏外动画优化、阴雨天气和30秒渐变按钮已交付；材质草地旧发布缺口关闭，150人及最终天气后续Shipping构建成功。人群休息抽查1例超时与成品实机验收待确认，编辑器150人约11.4FPS。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +679,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>查看近期50条聊天，读取32个新、更新或待确认来源聊天最新1–6回合；更早回合未全读，非全历史遍历。未列出聊天保留已确认基线。</x:v>
+        <x:v>查看近期50条聊天；新增2个项目目录聊天全部1和3回合，另读取32个待确认来源最新1回合，34次均成功。更早回合未全读，未列出已知聊天保留基线，不声称遍历全部历史。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -835,6 +835,18 @@
       <x:c r="D35" s="9"/>
       <x:c r="E35" s="9"/>
       <x:c r="F35" s="9"/>
+    </x:row>
+    <x:row r="36" ht="59" customHeight="1">
+      <x:c r="A36" s="20" t="n">
+        <x:v>46302.379791666666</x:v>
+      </x:c>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="9" t="str">
+        <x:v>150名White、四级LOD与屏外动画优化、阴雨天气和30秒渐变按钮已交付；材质草地旧发布缺口关闭，150人及最终天气后续Shipping构建成功。人群休息抽查1例超时与成品实机验收待确认，编辑器150人约11.4FPS。 新增16项，修订11项，进行中0项。</x:v>
+      </x:c>
+      <x:c r="D36" s="9"/>
+      <x:c r="E36" s="9"/>
+      <x:c r="F36" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -861,6 +873,8 @@
     <x:mergeCell ref="C34:F34"/>
     <x:mergeCell ref="A35:B35"/>
     <x:mergeCell ref="C35:F35"/>
+    <x:mergeCell ref="A36:B36"/>
+    <x:mergeCell ref="C36:F36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R7eb86a632ca34606"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rc013123803ba4d94"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -81,7 +81,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -348,7 +354,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -457,7 +463,7 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
@@ -467,7 +473,7 @@
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>角色、建筑与环境的材质、贴图、天空光照及渲染效果。</x:v>
@@ -478,7 +484,7 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
@@ -488,7 +494,7 @@
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -499,7 +505,7 @@
         <x:v>交互与AI</x:v>
       </x:c>
       <x:c r="B12" s="15" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="15" t="n">
         <x:v>0</x:v>
@@ -509,10 +515,10 @@
       </x:c>
       <x:c r="E12" s="15" t="n">
         <x:f>SUM(B12:D12)</x:f>
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>门交互部署、学生接入、寻路及人群避让。</x:v>
+        <x:v>门及灯光交互部署、学生接入、寻路及人群避让。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
@@ -520,7 +526,7 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
@@ -530,7 +536,7 @@
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -541,7 +547,7 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
@@ -551,7 +557,7 @@
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -604,17 +610,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -626,7 +632,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>218</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -634,11 +640,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>254</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -667,7 +673,7 @@
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>150名White、四级LOD与屏外动画优化、阴雨天气和30秒渐变按钮已交付；材质草地旧发布缺口关闭，150人及最终天气后续Shipping构建成功。人群休息抽查1例超时与成品实机验收待确认，编辑器150人约11.4FPS。</x:v>
+        <x:v>五栋楼254开关/161回路交付、508次E输入通过；动态雨景和原晴朗昼夜天空恢复，最终27测试通过。食堂广场810处材质保存及实例同步通过，雨景和食堂严格1:1仍有差异，新材质完整昼夜晴雨回归待确认。新增00:03 Shipping构建早于食堂改造。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
@@ -679,7 +685,7 @@
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>查看近期50条聊天；新增2个项目目录聊天全部1和3回合，另读取32个待确认来源最新1回合，34次均成功。更早回合未全读，未列出已知聊天保留基线，不声称遍历全部历史。</x:v>
+        <x:v>近期列表50条，41条项目目录聊天（含追踪）；3个新实施聊天读取全部2/6/3回合，34个旧待确认来源各读最新1回合。2个外部图片聊天仅读文本，未证实项目关联。旧更早回合及列表外已知聊天保留基线，未遍历全部历史。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -741,8 +747,8 @@
       <x:c r="F27" s="11"/>
     </x:row>
     <x:row r="28" ht="44" customHeight="1">
-      <x:c r="A28" s="20" t="n">
-        <x:v>46295.70775462963</x:v>
+      <x:c r="A28" s="20" t="d">
+        <x:v>2026-09-30T16:59:10.000Z</x:v>
       </x:c>
       <x:c r="B28" s="1"/>
       <x:c r="C28" s="9" t="str">
@@ -753,8 +759,8 @@
       <x:c r="F28" s="9"/>
     </x:row>
     <x:row r="29" ht="44" customHeight="1">
-      <x:c r="A29" s="20" t="n">
-        <x:v>46295.718298611115</x:v>
+      <x:c r="A29" s="20" t="d">
+        <x:v>2026-09-30T17:14:21.000Z</x:v>
       </x:c>
       <x:c r="B29" s="1"/>
       <x:c r="C29" s="9" t="str">
@@ -765,8 +771,8 @@
       <x:c r="F29" s="9"/>
     </x:row>
     <x:row r="30" ht="59" customHeight="1">
-      <x:c r="A30" s="20" t="n">
-        <x:v>46296.382731481484</x:v>
+      <x:c r="A30" s="20" t="d">
+        <x:v>2026-10-01T09:11:08.000Z</x:v>
       </x:c>
       <x:c r="B30" s="1"/>
       <x:c r="C30" s="9" t="str">
@@ -777,8 +783,8 @@
       <x:c r="F30" s="9"/>
     </x:row>
     <x:row r="31" ht="59" customHeight="1">
-      <x:c r="A31" s="20" t="n">
-        <x:v>46297.38238425926</x:v>
+      <x:c r="A31" s="20" t="d">
+        <x:v>2026-10-02T09:10:38.000Z</x:v>
       </x:c>
       <x:c r="B31" s="1"/>
       <x:c r="C31" s="9" t="str">
@@ -789,8 +795,8 @@
       <x:c r="F31" s="9"/>
     </x:row>
     <x:row r="32" ht="59" customHeight="1">
-      <x:c r="A32" s="20" t="n">
-        <x:v>46298.38186342592</x:v>
+      <x:c r="A32" s="20" t="d">
+        <x:v>2026-10-03T09:09:52.999Z</x:v>
       </x:c>
       <x:c r="B32" s="1"/>
       <x:c r="C32" s="9" t="str">
@@ -801,8 +807,8 @@
       <x:c r="F32" s="9"/>
     </x:row>
     <x:row r="33" ht="59" customHeight="1">
-      <x:c r="A33" s="20" t="n">
-        <x:v>46299.386030092595</x:v>
+      <x:c r="A33" s="20" t="d">
+        <x:v>2026-10-04T09:15:53.000Z</x:v>
       </x:c>
       <x:c r="B33" s="1"/>
       <x:c r="C33" s="9" t="str">
@@ -813,8 +819,8 @@
       <x:c r="F33" s="9"/>
     </x:row>
     <x:row r="34" ht="59" customHeight="1">
-      <x:c r="A34" s="20" t="n">
-        <x:v>46300.38545138889</x:v>
+      <x:c r="A34" s="20" t="d">
+        <x:v>2026-10-05T09:15:03.000Z</x:v>
       </x:c>
       <x:c r="B34" s="1"/>
       <x:c r="C34" s="9" t="str">
@@ -825,8 +831,8 @@
       <x:c r="F34" s="9"/>
     </x:row>
     <x:row r="35" ht="44" customHeight="1">
-      <x:c r="A35" s="20" t="n">
-        <x:v>46301.38113425926</x:v>
+      <x:c r="A35" s="20" t="d">
+        <x:v>2026-10-06T09:08:50.000Z</x:v>
       </x:c>
       <x:c r="B35" s="1"/>
       <x:c r="C35" s="9" t="str">
@@ -837,8 +843,8 @@
       <x:c r="F35" s="9"/>
     </x:row>
     <x:row r="36" ht="59" customHeight="1">
-      <x:c r="A36" s="20" t="n">
-        <x:v>46302.379791666666</x:v>
+      <x:c r="A36" s="20" t="d">
+        <x:v>2026-10-07T09:06:54.000Z</x:v>
       </x:c>
       <x:c r="B36" s="1"/>
       <x:c r="C36" s="9" t="str">
@@ -847,6 +853,18 @@
       <x:c r="D36" s="9"/>
       <x:c r="E36" s="9"/>
       <x:c r="F36" s="9"/>
+    </x:row>
+    <x:row r="37" ht="59" customHeight="1">
+      <x:c r="A37" s="20" t="d">
+        <x:v>2026-10-09T09:07:22.000Z</x:v>
+      </x:c>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="9" t="str">
+        <x:v>五栋楼254开关/161回路交付、508次E输入通过；动态雨景和原晴朗昼夜天空恢复，最终27测试通过。食堂广场810处材质保存及实例同步通过，雨景和食堂严格1:1仍有差异，新材质完整昼夜晴雨回归待确认。新增00:03 Shipping构建早于食堂改造。 新增27项，修订7项；无正在实施证据，进行中0项。</x:v>
+      </x:c>
+      <x:c r="D37" s="9"/>
+      <x:c r="E37" s="9"/>
+      <x:c r="F37" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -875,6 +893,8 @@
     <x:mergeCell ref="C35:F35"/>
     <x:mergeCell ref="A36:B36"/>
     <x:mergeCell ref="C36:F36"/>
+    <x:mergeCell ref="A37:B37"/>
+    <x:mergeCell ref="C37:F37"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/ProjectProgress/表格/CampusAuto项目进展.xlsx
+++ b/ProjectProgress/表格/CampusAuto项目进展.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="Rc013123803ba4d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" r:id="R0289729d0a5f4800"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -354,7 +354,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -463,7 +463,7 @@
         <x:v>材质渲染</x:v>
       </x:c>
       <x:c r="B10" s="15" t="n">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C10" s="15" t="n">
         <x:v>0</x:v>
@@ -473,7 +473,7 @@
       </x:c>
       <x:c r="E10" s="15" t="n">
         <x:f>SUM(B10:D10)</x:f>
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>角色、建筑与环境的材质、贴图、天空光照及渲染效果。</x:v>
@@ -484,7 +484,7 @@
         <x:v>场景问题</x:v>
       </x:c>
       <x:c r="B11" s="15" t="n">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C11" s="15" t="n">
         <x:v>0</x:v>
@@ -494,7 +494,7 @@
       </x:c>
       <x:c r="E11" s="15" t="n">
         <x:f>SUM(B11:D11)</x:f>
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>建筑、室内、景观、道路、布局及场景碰撞。</x:v>
@@ -505,7 +505,7 @@
         <x:v>交互与AI</x:v>
       </x:c>
       <x:c r="B12" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="15" t="n">
         <x:v>0</x:v>
@@ -515,7 +515,7 @@
       </x:c>
       <x:c r="E12" s="15" t="n">
         <x:f>SUM(B12:D12)</x:f>
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>门及灯光交互部署、学生接入、寻路及人群避让。</x:v>
@@ -526,7 +526,7 @@
         <x:v>代码问题</x:v>
       </x:c>
       <x:c r="B13" s="15" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="15" t="n">
         <x:v>0</x:v>
@@ -536,7 +536,7 @@
       </x:c>
       <x:c r="E13" s="15" t="n">
         <x:f>SUM(B13:D13)</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>蓝图逻辑、输入、运行时挂接、实例化和历史脚本。</x:v>
@@ -547,7 +547,7 @@
         <x:v>资产管理</x:v>
       </x:c>
       <x:c r="B14" s="15" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="15" t="n">
         <x:v>0</x:v>
@@ -557,7 +557,7 @@
       </x:c>
       <x:c r="E14" s="15" t="n">
         <x:f>SUM(B14:D14)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>资产分类、导入导出、引用、归档和源清单一致性。</x:v>
@@ -574,11 +574,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="15" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
         <x:f>SUM(B15:D15)</x:f>
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>帧耗、显存、缓存、保存同步及性能目标。</x:v>
@@ -610,17 +610,17 @@
         <x:v>测试验收</x:v>
       </x:c>
       <x:c r="B17" s="15" t="n">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="15" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
         <x:f>SUM(B17:D17)</x:f>
-        <x:v>73</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>运行回归、碰撞通行、保存持久性及验收范围。</x:v>
@@ -632,7 +632,7 @@
       </x:c>
       <x:c r="B18" s="16" t="n">
         <x:f>SUM(B8:B17)</x:f>
-        <x:v>242</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C18" s="16" t="n">
         <x:f>SUM(C8:C17)</x:f>
@@ -640,11 +640,11 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>SUM(D8:D17)</x:f>
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>SUM(E8:E17)</x:f>
-        <x:v>281</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="F18" s="12"/>
     </x:row>
@@ -668,24 +668,24 @@
       <x:c r="E20" s="18"/>
       <x:c r="F20" s="18"/>
     </x:row>
-    <x:row r="21" ht="44" customHeight="1">
+    <x:row r="21" ht="59" customHeight="1">
       <x:c r="A21" s="17" t="str">
         <x:v>最近检查</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>五栋楼254开关/161回路交付、508次E输入通过；动态雨景和原晴朗昼夜天空恢复，最终27测试通过。食堂广场810处材质保存及实例同步通过，雨景和食堂严格1:1仍有差异，新材质完整昼夜晴雨回归待确认。新增00:03 Shipping构建早于食堂改造。</x:v>
+        <x:v>灯光补齐1195真实灯并默认关闭，15点30次E输入及161回路通过；同类石板全场替换旧残留0，雨停水渍渐干通过，原天气缺口收窄至夜景往返。A/B48教室合为24间并完成统一室内重做，局部门碰撞昼夜开关通过；PS5配置完成、实体USB/蓝牙及教室性能/严格参考验收待确认。新增两批Shipping早于教室重做。</x:v>
       </x:c>
       <x:c r="C21" s="18"/>
       <x:c r="D21" s="18"/>
       <x:c r="E21" s="18"/>
       <x:c r="F21" s="18"/>
     </x:row>
-    <x:row r="22" ht="44" customHeight="1">
+    <x:row r="22" ht="59" customHeight="1">
       <x:c r="A22" s="17" t="str">
         <x:v>来源范围</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>近期列表50条，41条项目目录聊天（含追踪）；3个新实施聊天读取全部2/6/3回合，34个旧待确认来源各读最新1回合。2个外部图片聊天仅读文本，未证实项目关联。旧更早回合及列表外已知聊天保留基线，未遍历全部历史。</x:v>
+        <x:v>近期列表50条，40条项目ID或目录关联聊天（含本追踪）；3个新实施及2个更新聊天读取全部1/1/2/4/3回合，35个旧待确认来源各读最新1回合，更新时间和回合均与基线一致。另读1个外部教室图片聊天全部2回合，文本未明确项目关联。列表外旧聊天按已存ID复读或保留基线，更早回合未全读，不声称遍历全部历史。</x:v>
       </x:c>
       <x:c r="C22" s="18"/>
       <x:c r="D22" s="18"/>
@@ -865,6 +865,18 @@
       <x:c r="D37" s="9"/>
       <x:c r="E37" s="9"/>
       <x:c r="F37" s="9"/>
+    </x:row>
+    <x:row r="38" ht="74" customHeight="1">
+      <x:c r="A38" s="20" t="d">
+        <x:v>2026-10-10T09:11:56.000Z</x:v>
+      </x:c>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="9" t="str">
+        <x:v>灯光补齐1195真实灯并默认关闭，15点30次E输入及161回路通过；同类石板全场替换旧残留0，雨停水渍渐干通过，原天气缺口收窄至夜景往返。A/B48教室合为24间并完成统一室内重做，局部门碰撞昼夜开关通过；PS5配置完成、实体USB/蓝牙及教室性能/严格参考验收待确认。新增两批Shipping早于教室重做。 新增29项，修订15项；无仍在实施证据，进行中0。</x:v>
+      </x:c>
+      <x:c r="D38" s="9"/>
+      <x:c r="E38" s="9"/>
+      <x:c r="F38" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -895,6 +907,8 @@
     <x:mergeCell ref="C36:F36"/>
     <x:mergeCell ref="A37:B37"/>
     <x:mergeCell ref="C37:F37"/>
+    <x:mergeCell ref="A38:B38"/>
+    <x:mergeCell ref="C38:F38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
